--- a/target/classes/main/template/template.xlsx
+++ b/target/classes/main/template/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IdeaProjects\Java-ParserWeather\src\main\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F15FA5-6C30-4E18-B821-407008E74E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692F1B1F-EEA6-446F-BA1D-0383C23E13AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Данные_фактические" sheetId="1" r:id="rId1"/>
